--- a/examples/longrui_bill_核算.xlsx
+++ b/examples/longrui_bill_核算.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:L4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -475,11 +475,6 @@
       <c r="L1" t="inlineStr">
         <is>
           <t>核算人工费</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>核算措施费</t>
         </is>
       </c>
     </row>
@@ -531,9 +526,6 @@
       <c r="L2" t="n">
         <v>1896.37</v>
       </c>
-      <c r="M2" t="n">
-        <v>527.27</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -582,9 +574,6 @@
       </c>
       <c r="L3" t="n">
         <v>5051.97</v>
-      </c>
-      <c r="M3" t="n">
-        <v>4937.07</v>
       </c>
     </row>
     <row r="4">
@@ -640,9 +629,6 @@
       <c r="L4" t="n">
         <v>1900.38</v>
       </c>
-      <c r="M4" t="n">
-        <v>1574.53</v>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
